--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:51</t>
+          <t>2026-05-05 20:19</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$73</definedName>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>
@@ -2701,14 +2701,14 @@
         <v>3750</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>26250</v>
+        <v>22500</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ (manual — ไม่มีใน GPS) (+7,500฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,750฿)</t>
         </is>
       </c>
     </row>
@@ -3148,19 +3148,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>
@@ -602,10 +602,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
@@ -678,19 +678,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
@@ -830,19 +830,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -868,19 +868,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>11250</v>
+        <v>10913</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>0</v>
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1020,19 +1020,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -1096,19 +1096,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
@@ -1134,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1172,19 +1172,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
@@ -1210,19 +1210,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
@@ -1438,19 +1438,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1476,19 +1476,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1704,19 +1704,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1780,19 +1780,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -1856,19 +1856,19 @@
         <v>1</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>11250</v>
+        <v>9900</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -2236,19 +2236,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>11250</v>
+        <v>9900</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -2350,19 +2350,19 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2388,19 +2388,19 @@
         <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2426,19 +2426,19 @@
         <v>3</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>30000</v>
+        <v>26400</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -2464,19 +2464,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
@@ -2502,19 +2502,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -2578,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -2616,19 +2616,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -2692,23 +2692,23 @@
         <v>2</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>22500</v>
+        <v>20500</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,750฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250฿)</t>
         </is>
       </c>
     </row>
@@ -2730,10 +2730,10 @@
         <v>2</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -2768,19 +2768,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
@@ -2806,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -2844,19 +2844,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
@@ -2958,19 +2958,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         <v>1</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
@@ -3034,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -3148,19 +3148,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -109,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -602,10 +602,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
@@ -678,19 +678,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
@@ -830,19 +830,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>3638</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>10913</v>
+        <v>10914.69</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>0</v>
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1020,19 +1020,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -1096,19 +1096,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
@@ -1134,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1172,19 +1172,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
@@ -1210,19 +1210,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
@@ -1438,19 +1438,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1476,19 +1476,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1704,19 +1704,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1780,19 +1780,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -1856,19 +1856,19 @@
         <v>1</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>9900</v>
+        <v>9968.860000000001</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -2236,19 +2236,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>9900</v>
+        <v>9968.860000000001</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -2350,19 +2350,19 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>19800</v>
+        <v>19936.72</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2388,19 +2388,19 @@
         <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>19800</v>
+        <v>19936.72</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2426,19 +2426,19 @@
         <v>3</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>19800</v>
+        <v>19937.58</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>26400</v>
+        <v>26582.58</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -2464,19 +2464,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
@@ -2502,19 +2502,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -2578,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -2616,19 +2616,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -2692,23 +2692,23 @@
         <v>2</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>14000</v>
+        <v>14046</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>20500</v>
+        <v>20592</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
         </is>
       </c>
     </row>
@@ -3148,19 +3148,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -3130,84 +3130,8 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G72" s="10" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H72" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="10" t="n">
-        <v>11148.03</v>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>11148.03</v>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J73"/>
+  <autoFilter ref="A4:J71"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>6546.17</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>14046</v>
+        <v>6546.17</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>3273</v>
@@ -2704,11 +2704,11 @@
         <v>3273</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>20592</v>
+        <v>13092</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -586,26 +586,26 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7276.69</v>
+        <v>6546.17</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14553.38</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -614,21 +614,21 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>14553.38</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+0.00฿)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46121</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -637,60 +637,60 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>14553.38</v>
+        <v>7432.03</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>14553.38</v>
+        <v>11148.03</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46123</v>
+        <v>46143</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10274.81</v>
+        <v>11148.03</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -700,11 +700,11 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46122</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -713,112 +713,112 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>14553.38</v>
+        <v>7432.03</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>14553.38</v>
+        <v>11148.03</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46122</v>
+        <v>46144</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14553.38</v>
+        <v>7432.03</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>14553.38</v>
+        <v>11148.03</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>14553.38</v>
+        <v>7432.03</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>14553.38</v>
+        <v>11148.03</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46123</v>
+        <v>46145</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -830,19 +830,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>10274.81</v>
+        <v>11148.03</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -852,11 +852,11 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -868,19 +868,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>3638</v>
+        <v>3716</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>10914.69</v>
+        <v>11148.03</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -890,35 +890,35 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46123</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -941,60 +941,60 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13699.62</v>
+        <v>7432.03</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>13699.62</v>
+        <v>11148.03</v>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1004,35 +1004,35 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46124</v>
+        <v>46147</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
@@ -1042,49 +1042,49 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46124</v>
+        <v>46147</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>14612.94</v>
+        <v>7432.03</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>14612.94</v>
+        <v>11148.03</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1096,19 +1096,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
@@ -1118,11 +1118,11 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46124</v>
+        <v>46148</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1134,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1156,11 +1156,11 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1169,36 +1169,36 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>7306.47</v>
+        <v>14864.06</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>10959.47</v>
+        <v>14864.06</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1207,32 +1207,32 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7306.47</v>
+        <v>14864.06</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>10959.47</v>
+        <v>14864.06</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>10959.47</v>
+        <v>11148.03</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
@@ -1270,49 +1270,49 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>21919.41</v>
+        <v>7432.03</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>21919.41</v>
+        <v>11148.03</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1321,36 +1321,36 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>7306.47</v>
+        <v>14864.06</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>10959.47</v>
+        <v>14864.06</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1359,98 +1359,98 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>14612.94</v>
+        <v>7432.03</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>14612.94</v>
+        <v>11148.03</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46125</v>
+        <v>46151</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>14612.94</v>
+        <v>7322.2</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>14612.94</v>
+        <v>10983.2</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3653</v>
+        <v>3661</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10959.47</v>
+        <v>10983.2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1460,11 +1460,11 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1473,36 +1473,36 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>7306.47</v>
+        <v>14644.4</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>10959.47</v>
+        <v>14644.4</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46126</v>
+        <v>46150</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1511,13 +1511,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>21919.41</v>
+        <v>14644.4</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -1526,83 +1526,83 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>21919.41</v>
+        <v>14644.4</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>14612.94</v>
+        <v>7322.2</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>14612.94</v>
+        <v>10983.2</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46126</v>
+        <v>46151</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3653</v>
+        <v>3661</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10959.47</v>
+        <v>10983.2</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46127</v>
+        <v>46152</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -1625,36 +1625,36 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>21919.41</v>
+        <v>7322.2</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>21919.41</v>
+        <v>10983.2</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46128</v>
+        <v>46151</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1666,19 +1666,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3425</v>
+        <v>3661</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10274.81</v>
+        <v>10983.2</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1688,35 +1688,35 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46128</v>
+        <v>46152</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3425</v>
+        <v>3661</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>10274.81</v>
+        <v>10983.2</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
@@ -1726,26 +1726,26 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46127</v>
+        <v>46152</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14612.94</v>
+        <v>14644.4</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14612.94</v>
+        <v>14644.4</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1764,11 +1764,11 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46127</v>
+        <v>46152</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -1780,19 +1780,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>3653</v>
+        <v>3661</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>10959.47</v>
+        <v>10983.2</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
@@ -1802,26 +1802,26 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46128</v>
+        <v>46153</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>13699.62</v>
+        <v>14644.4</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>13699.62</v>
+        <v>14644.4</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -1840,49 +1840,49 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46129</v>
+        <v>46153</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>6645.86</v>
+        <v>7322.2</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>6645.86</v>
+        <v>14644.4</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>3323</v>
+        <v>0</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>9968.860000000001</v>
+        <v>14644.4</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46128</v>
+        <v>46153</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>13699.62</v>
+        <v>14644.4</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>13699.62</v>
+        <v>14644.4</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -1916,87 +1916,87 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46128</v>
+        <v>46154</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>6849.81</v>
+        <v>7322.2</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>13699.62</v>
+        <v>7322.2</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>13699.62</v>
+        <v>10983.2</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>13699.62</v>
+        <v>7432.03</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>13699.62</v>
+        <v>11148.03</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46129</v>
+        <v>46154</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -2008,10 +2008,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>6645.86</v>
+        <v>7322.2</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>13291.72</v>
+        <v>14644.4</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>13291.72</v>
+        <v>14644.4</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2030,26 +2030,26 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>6645.86</v>
+        <v>7432.03</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -2068,26 +2068,26 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>6645.86</v>
+        <v>7432.03</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2106,11 +2106,11 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2122,10 +2122,10 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>6645.86</v>
+        <v>7432.03</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>13291.72</v>
+        <v>14864.06</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -2144,64 +2144,64 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>13291.72</v>
+        <v>7543.52</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>13291.72</v>
+        <v>11315.52</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46131</v>
+        <v>46156</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -2220,35 +2220,35 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46131</v>
+        <v>46156</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3323</v>
+        <v>3772</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>9968.860000000001</v>
+        <v>11315.52</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2258,11 +2258,11 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>46131</v>
+        <v>46156</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2271,51 +2271,51 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>13291.72</v>
+        <v>7543.52</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>13291.72</v>
+        <v>11315.52</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46131</v>
+        <v>46157</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -2334,11 +2334,11 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>46132</v>
+        <v>46157</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -2350,19 +2350,19 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>6645</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>19936.72</v>
+        <v>15087.04</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2372,35 +2372,35 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46132</v>
+        <v>46158</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>13291.72</v>
+        <v>15087.04</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>6645</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>19936.72</v>
+        <v>15087.04</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2410,11 +2410,11 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46132</v>
+        <v>46158</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -2423,74 +2423,74 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>19937.58</v>
+        <v>7543.52</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>6645</v>
+        <v>3772</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>26582.58</v>
+        <v>11315.52</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46133</v>
+        <v>46159</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>6546.17</v>
+        <v>15087.04</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>9819.17</v>
+        <v>15087.04</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46134</v>
+        <v>46159</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2499,36 +2499,36 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6546.17</v>
+        <v>15087.04</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>9819.17</v>
+        <v>15087.04</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46134</v>
+        <v>46160</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -2540,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3273</v>
+        <v>3772</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>9819.17</v>
+        <v>11315.52</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -2562,11 +2562,11 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>46134</v>
+        <v>46159</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2575,98 +2575,98 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>6546.17</v>
+        <v>15087.04</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>9819.17</v>
+        <v>15087.04</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46135</v>
+        <v>46160</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>6546.17</v>
+        <v>7543.52</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>6546.17</v>
+        <v>15087.04</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>9819.17</v>
+        <v>15087.04</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>46134</v>
+        <v>46161</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3273</v>
+        <v>3828</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>9819.17</v>
+        <v>11484.67</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -2676,111 +2676,111 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46134</v>
+        <v>46161</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3273</v>
+        <v>3828</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>13092</v>
+        <v>11484.67</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>46137</v>
+        <v>46161</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>13000</v>
+        <v>7656.67</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>13000</v>
+        <v>11484.67</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46137</v>
+        <v>46161</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
@@ -2790,35 +2790,35 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>46138</v>
+        <v>46161</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -2828,49 +2828,49 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46137</v>
+        <v>46161</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>6500</v>
+        <v>15313.34</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="H64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>9750</v>
+        <v>15313.34</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>46138</v>
+        <v>46162</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2879,36 +2879,36 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>13000</v>
+        <v>7656.67</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>13000</v>
+        <v>11484.67</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46138</v>
+        <v>46161</v>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -2920,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>13000</v>
+        <v>15313.34</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>13000</v>
+        <v>15313.34</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
@@ -2942,35 +2942,35 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>46138</v>
+        <v>46162</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -2980,11 +2980,11 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -2993,60 +2993,60 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>6500</v>
+        <v>22970.01</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="H68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>9750</v>
+        <v>22970.01</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -3056,35 +3056,35 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46141</v>
+        <v>46163</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
@@ -3094,11 +3094,11 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>46141</v>
+        <v>46163</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>9750</v>
+        <v>11484.67</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -3130,8 +3130,1794 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="10" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="7" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="10" t="n">
+        <v>15313.34</v>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>11484.67</v>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>22630.56</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="10" t="n">
+        <v>22630.56</v>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="10" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <v>15087.04</v>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="7" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="10" t="n">
+        <v>11315.52</v>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J71"/>
+  <autoFilter ref="A4:J118"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6546.17</v>
+        <v>6500</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -640,19 +640,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
@@ -678,19 +678,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -716,19 +716,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
@@ -754,19 +754,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -792,19 +792,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
@@ -830,19 +830,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -868,19 +868,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -944,19 +944,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1020,19 +1020,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
@@ -1058,19 +1058,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -1096,19 +1096,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
@@ -1134,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>0</v>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
@@ -1286,19 +1286,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
@@ -1362,19 +1362,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1400,19 +1400,19 @@
         <v>1</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
@@ -1438,19 +1438,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         <v>2</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1552,19 +1552,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -1628,19 +1628,19 @@
         <v>1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1704,19 +1704,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1780,19 +1780,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -1932,19 +1932,19 @@
         <v>1</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>10983.2</v>
+        <v>10920</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>11148.03</v>
+        <v>11066.5</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>14644.4</v>
+        <v>14560</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>14864.06</v>
+        <v>14755</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -2160,19 +2160,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -2236,19 +2236,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2274,19 +2274,19 @@
         <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2426,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -2692,19 +2692,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
@@ -2730,19 +2730,19 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -2768,19 +2768,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
@@ -2806,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>2</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
@@ -2882,19 +2882,19 @@
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
@@ -2958,19 +2958,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
         <v>3</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>22970.01</v>
+        <v>22717.5</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>22970.01</v>
+        <v>22717.5</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
@@ -3034,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -3224,19 +3224,19 @@
         <v>1</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -3300,19 +3300,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
@@ -3338,19 +3338,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -3376,19 +3376,19 @@
         <v>1</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H78" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>2</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -3452,19 +3452,19 @@
         <v>1</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
@@ -3490,19 +3490,19 @@
         <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -3528,19 +3528,19 @@
         <v>1</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H82" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -3604,19 +3604,19 @@
         <v>1</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
@@ -3642,19 +3642,19 @@
         <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         <v>2</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
@@ -3718,19 +3718,19 @@
         <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         <v>2</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         <v>2</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         <v>2</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>15313.34</v>
+        <v>15145</v>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
@@ -3870,19 +3870,19 @@
         <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>11484.67</v>
+        <v>11358.5</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -3908,19 +3908,19 @@
         <v>1</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
@@ -3946,19 +3946,19 @@
         <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -3984,19 +3984,19 @@
         <v>1</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
@@ -4022,19 +4022,19 @@
         <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -4060,19 +4060,19 @@
         <v>1</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
@@ -4098,19 +4098,19 @@
         <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -4136,19 +4136,19 @@
         <v>1</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
@@ -4174,19 +4174,19 @@
         <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -4212,19 +4212,19 @@
         <v>1</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
@@ -4250,19 +4250,19 @@
         <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -4288,19 +4288,19 @@
         <v>1</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         <v>2</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
         <v>2</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
@@ -4402,19 +4402,19 @@
         <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
@@ -4440,19 +4440,19 @@
         <v>1</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
         <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
@@ -4490,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
         <v>2</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="G108" s="10" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>15087.04</v>
+        <v>14950</v>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
@@ -4554,19 +4554,19 @@
         <v>1</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>22630.56</v>
+        <v>22425</v>
       </c>
       <c r="G110" s="10" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>22630.56</v>
+        <v>22425</v>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
@@ -4630,19 +4630,19 @@
         <v>1</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11315.52</v>
+        <v>11213</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
         <v>2</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>15087.04</v>
+        <v>14755</v>
       </c>
       <c r="G112" s="10" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>15087.04</v>
+        <v>14755</v>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
@@ -4706,10 +4706,10 @@
         <v>2</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>15087.04</v>
+        <v>14755</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>0</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>15087.04</v>
+        <v>14755</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
@@ -4744,19 +4744,19 @@
         <v>1</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="H114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>11315.52</v>
+        <v>11066.5</v>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
         <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>11315.52</v>
+        <v>11066.5</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
@@ -4820,19 +4820,19 @@
         <v>1</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="H116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>11315.52</v>
+        <v>11066.5</v>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
@@ -4858,19 +4858,19 @@
         <v>1</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>11315.52</v>
+        <v>11066.5</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
@@ -4896,19 +4896,19 @@
         <v>1</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="H118" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>11315.52</v>
+        <v>11066.5</v>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -640,19 +640,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
@@ -678,19 +678,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -716,19 +716,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
@@ -754,19 +754,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -792,19 +792,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
@@ -830,19 +830,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -868,19 +868,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -944,19 +944,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1020,19 +1020,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
@@ -1058,19 +1058,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -1096,19 +1096,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
@@ -1134,19 +1134,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>0</v>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
@@ -1286,19 +1286,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
@@ -1362,19 +1362,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1400,19 +1400,19 @@
         <v>1</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
@@ -1438,19 +1438,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         <v>2</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1552,19 +1552,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -1628,19 +1628,19 @@
         <v>1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1704,19 +1704,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1780,19 +1780,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -1932,19 +1932,19 @@
         <v>1</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -2160,19 +2160,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -2236,19 +2236,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2274,19 +2274,19 @@
         <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2426,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -2692,19 +2692,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
@@ -2730,19 +2730,19 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -2768,19 +2768,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
@@ -2806,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>2</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
@@ -2882,19 +2882,19 @@
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
@@ -2958,19 +2958,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
         <v>3</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>22717.5</v>
+        <v>22368</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>22717.5</v>
+        <v>22368</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
@@ -3034,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -3224,19 +3224,19 @@
         <v>1</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -3300,19 +3300,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
@@ -3338,19 +3338,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -3376,19 +3376,19 @@
         <v>1</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H78" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>2</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -3452,19 +3452,19 @@
         <v>1</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
@@ -3490,19 +3490,19 @@
         <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -3528,19 +3528,19 @@
         <v>1</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H82" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -3604,19 +3604,19 @@
         <v>1</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
@@ -3642,19 +3642,19 @@
         <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         <v>2</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
@@ -3718,19 +3718,19 @@
         <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         <v>2</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         <v>2</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         <v>2</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
@@ -3870,19 +3870,19 @@
         <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -3908,19 +3908,19 @@
         <v>1</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
@@ -3946,19 +3946,19 @@
         <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -3984,19 +3984,19 @@
         <v>1</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
@@ -4022,19 +4022,19 @@
         <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -4060,19 +4060,19 @@
         <v>1</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
@@ -4098,19 +4098,19 @@
         <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -4136,19 +4136,19 @@
         <v>1</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
@@ -4174,19 +4174,19 @@
         <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -4212,19 +4212,19 @@
         <v>1</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
@@ -4250,19 +4250,19 @@
         <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -4288,19 +4288,19 @@
         <v>1</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         <v>2</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
         <v>2</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
@@ -4402,19 +4402,19 @@
         <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
@@ -4440,19 +4440,19 @@
         <v>1</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
         <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
@@ -4490,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
         <v>2</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G108" s="10" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
@@ -4554,19 +4554,19 @@
         <v>1</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="G110" s="10" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
@@ -4630,19 +4630,19 @@
         <v>1</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
         <v>2</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G112" s="10" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
@@ -4706,10 +4706,10 @@
         <v>2</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>0</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
@@ -4744,19 +4744,19 @@
         <v>1</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
         <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
@@ -4820,19 +4820,19 @@
         <v>1</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
@@ -4858,19 +4858,19 @@
         <v>1</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
@@ -4896,19 +4896,19 @@
         <v>1</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H118" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -675,32 +675,32 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -713,26 +713,26 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -751,32 +751,32 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46146</v>
+        <v>46144</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -808,13 +808,13 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -827,41 +827,41 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
@@ -884,17 +884,17 @@
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -998,17 +998,17 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1150,13 +1150,13 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -1226,83 +1226,83 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14528</v>
+        <v>0</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -1378,83 +1378,83 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46151</v>
+        <v>46149</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3584</v>
+        <v>3632</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>10752</v>
+        <v>10896</v>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3584</v>
+        <v>3632</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10752</v>
+        <v>10896</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1464,35 +1464,35 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1502,88 +1502,88 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
@@ -1606,45 +1606,45 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -1682,60 +1682,60 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46153</v>
+        <v>46152</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1815,64 +1815,64 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46153</v>
+        <v>46152</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1882,45 +1882,45 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -1929,64 +1929,64 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>10896</v>
+        <v>10752</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2046,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>14528</v>
+        <v>14336</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2058,36 +2058,36 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>14528</v>
+        <v>14336</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>14528</v>
+        <v>14336</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>0</v>
@@ -2096,11 +2096,11 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>14528</v>
+        <v>14336</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2110,45 +2110,45 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -2160,48 +2160,48 @@
         <v>1</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>11040</v>
+        <v>10896</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>14720</v>
+        <v>14528</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -2210,11 +2210,11 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>14720</v>
+        <v>14528</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2262,45 +2262,45 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -2309,32 +2309,32 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
@@ -2366,17 +2366,17 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -2385,74 +2385,74 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -2461,74 +2461,74 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -2537,32 +2537,32 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
@@ -2654,29 +2654,29 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11184</v>
+        <v>11040</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
@@ -2689,32 +2689,32 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>3728</v>
+        <v>7360</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>11184</v>
+        <v>7360</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
@@ -2730,33 +2730,33 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>11184</v>
+        <v>11040</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -2768,33 +2768,33 @@
         <v>1</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>11184</v>
+        <v>11040</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -2803,36 +2803,36 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7456</v>
+        <v>14720</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11184</v>
+        <v>14720</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -2841,64 +2841,64 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>14912</v>
+        <v>7360</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>14912</v>
+        <v>11040</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>11184</v>
+        <v>11040</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2908,45 +2908,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2955,36 +2955,36 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -2993,36 +2993,36 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>22368</v>
+        <v>7456</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>22368</v>
+        <v>11184</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -3050,60 +3050,60 @@
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -3164,13 +3164,13 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
@@ -3183,32 +3183,32 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
@@ -3240,55 +3240,55 @@
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -3297,36 +3297,36 @@
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -3392,60 +3392,60 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -3563,79 +3563,79 @@
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3734,17 +3734,17 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -3753,112 +3753,112 @@
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H88" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46167</v>
+        <v>46165</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -3886,17 +3886,17 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -3905,74 +3905,74 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>7360</v>
+        <v>14912</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>11040</v>
+        <v>14912</v>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46169</v>
+        <v>46166</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -3981,74 +3981,74 @@
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>7360</v>
+        <v>14912</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>11040</v>
+        <v>14912</v>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>46169</v>
+        <v>46166</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7360</v>
+        <v>14912</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11040</v>
+        <v>14912</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -4060,33 +4060,33 @@
         <v>1</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -4098,105 +4098,105 @@
         <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7360</v>
+        <v>14912</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>11040</v>
+        <v>14912</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
@@ -4247,41 +4247,41 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -4323,74 +4323,74 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>14720</v>
+        <v>0</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="H104" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -4399,41 +4399,41 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
       <c r="H105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
@@ -4456,17 +4456,17 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -4475,36 +4475,36 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -4513,41 +4513,41 @@
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
@@ -4570,17 +4570,17 @@
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -4589,74 +4589,74 @@
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>22080</v>
+        <v>7360</v>
       </c>
       <c r="G110" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H110" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>22080</v>
+        <v>11040</v>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 3 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>46172</v>
+        <v>46170</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -4668,10 +4668,10 @@
         <v>2</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>14528</v>
+        <v>14720</v>
       </c>
       <c r="G112" s="10" t="n">
         <v>0</v>
@@ -4680,21 +4680,21 @@
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>14528</v>
+        <v>14720</v>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>46172</v>
+        <v>46170</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -4703,74 +4703,74 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>14528</v>
+        <v>7360</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H113" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>14528</v>
+        <v>11040</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ 50% (วันงาน 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>46172</v>
+        <v>46170</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>3632</v>
+        <v>3680</v>
       </c>
       <c r="H114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>10896</v>
+        <v>11040</v>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>46173</v>
+        <v>46171</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -4779,74 +4779,74 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7264</v>
+        <v>14720</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>10896</v>
+        <v>14720</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>46173</v>
+        <v>46171</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>7264</v>
+        <v>14720</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>10896</v>
+        <v>14720</v>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>46173</v>
+        <v>46171</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -4855,69 +4855,449 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>7264</v>
+        <v>14720</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>10896</v>
+        <v>14720</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>14720</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="10" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="7" t="n">
+        <v>11040</v>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="H120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="10" t="n">
+        <v>10896</v>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>14528</v>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="7" t="n">
+        <v>14528</v>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="H122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="10" t="n">
+        <v>10896</v>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>3632</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="7" t="n">
+        <v>10896</v>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>14528</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="10" t="n">
+        <v>14528</v>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
         <v>46173</v>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>14528</v>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="7" t="n">
+        <v>14528</v>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="H126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="10" t="n">
+        <v>10896</v>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>3632</v>
+      </c>
+      <c r="H127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="7" t="n">
+        <v>10896</v>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
         <is>
           <t>72-1217</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>LCB</t>
         </is>
       </c>
-      <c r="D118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F118" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="G118" s="10" t="n">
+      <c r="D128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="G128" s="10" t="n">
         <v>3632</v>
       </c>
-      <c r="H118" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="10" t="n">
+      <c r="H128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="10" t="n">
         <v>10896</v>
       </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J118"/>
+  <autoFilter ref="A4:J128"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>
@@ -649,14 +649,14 @@
         <v>3632</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -1827,14 +1827,14 @@
         <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -1941,14 +1941,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>14336</v>
+        <v>17920</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -3119,14 +3119,14 @@
         <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3157,14 +3157,14 @@
         <v>0</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3233,14 +3233,14 @@
         <v>3728</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3309,14 +3309,14 @@
         <v>0</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3613,14 +3613,14 @@
         <v>0</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>
@@ -611,14 +611,14 @@
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+0.00฿)</t>
+          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -646,17 +646,17 @@
         <v>7264</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>14528</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -3116,17 +3116,17 @@
         <v>7456</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3728</v>
+        <v>7456</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
         <v>14912</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว) (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3183,26 +3183,26 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I73" s="7" t="n">
         <v>14912</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Audit_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_Log'!$A$4:$J$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>
@@ -586,39 +586,39 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6500</v>
+        <v>7264</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>3250</v>
+        <v>14528</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -628,22 +628,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>7264</v>
@@ -652,26 +652,26 @@
         <v>0</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -789,64 +789,64 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -928,16 +928,16 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1080,11 +1080,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1131,26 +1131,26 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1194,11 +1194,11 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1270,39 +1270,39 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>14528</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1321,26 +1321,26 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -1422,35 +1422,35 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10896</v>
+        <v>10752</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1502,35 +1502,35 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -1549,64 +1549,64 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -1625,26 +1625,26 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1654,35 +1654,35 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -1726,39 +1726,39 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -1789,14 +1789,14 @@
         <v>3584</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
@@ -1827,29 +1827,29 @@
         <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1891,26 +1891,26 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n">
         <v>3584</v>
       </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="7" t="n">
-        <v>10752</v>
+        <v>17920</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -1920,73 +1920,73 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>7168</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>17920</v>
+        <v>10752</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
@@ -2068,39 +2068,39 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>14336</v>
+        <v>7264</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>14336</v>
+        <v>10896</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2148,73 +2148,73 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>14528</v>
+        <v>7360</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>14528</v>
+        <v>11040</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -2233,26 +2233,26 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2271,26 +2271,26 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2300,73 +2300,73 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -2385,26 +2385,26 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -2423,26 +2423,26 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
@@ -2486,39 +2486,39 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
@@ -2562,16 +2562,16 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
@@ -2613,26 +2613,26 @@
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2651,26 +2651,26 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2680,50 +2680,50 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -2765,26 +2765,26 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -2803,26 +2803,26 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
@@ -2866,35 +2866,35 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2955,26 +2955,26 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -3022,63 +3022,63 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>0</v>
+        <v>7456</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -3107,26 +3107,26 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -3145,26 +3145,26 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>3728</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>18640</v>
+        <v>14912</v>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
@@ -3233,52 +3233,52 @@
         <v>3728</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="n">
         <v>3728</v>
       </c>
-      <c r="H75" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I75" s="7" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -3297,26 +3297,26 @@
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -3436,16 +3436,16 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -3563,26 +3563,26 @@
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n">
         <v>3728</v>
       </c>
-      <c r="H83" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I83" s="7" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -3592,73 +3592,73 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -3677,26 +3677,26 @@
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
@@ -3816,16 +3816,16 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -3867,26 +3867,26 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -3905,26 +3905,26 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -3943,26 +3943,26 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
@@ -4006,39 +4006,39 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -4124,73 +4124,73 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>14912</v>
+        <v>7360</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>14912</v>
+        <v>11040</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
@@ -4209,26 +4209,26 @@
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
       <c r="H100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -4247,26 +4247,26 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -4314,50 +4314,50 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
       <c r="H103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -4399,26 +4399,26 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
@@ -4538,16 +4538,16 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -4589,26 +4589,26 @@
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G110" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H110" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -4665,26 +4665,26 @@
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H112" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4728,39 +4728,39 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -4884,69 +4884,69 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H118" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>11040</v>
+        <v>10896</v>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -4969,26 +4969,26 @@
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G120" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H120" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -5007,26 +5007,26 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
@@ -5074,50 +5074,50 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H123" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -5159,26 +5159,26 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H125" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
@@ -5258,46 +5258,8 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="G128" s="10" t="n">
-        <v>3632</v>
-      </c>
-      <c r="H128" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="10" t="n">
-        <v>10896</v>
-      </c>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J128"/>
+  <autoFilter ref="A4:J127"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -4665,26 +4665,26 @@
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H112" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>11040</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บ [override: exclude_50] — รถไม่ได้วิ่งจริง — ตัดเที่ยวเดียวของวันออกจาก base แล้ว เหลือ 0 เที่ยว แต่ GPS เห็นรถที่โรงงาน → กัน no_finish 100% ลั่น (คู่กับ remove_matched_trips ใน oatside_config.json)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/04_Audit_Log.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
